--- a/artfynd/A 34593-2024 artfynd.xlsx
+++ b/artfynd/A 34593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119541197</v>
+        <v>119541278</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729154</v>
+        <v>729224</v>
       </c>
       <c r="R2" t="n">
-        <v>7389019</v>
+        <v>7389317</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119541212</v>
+        <v>119541279</v>
       </c>
       <c r="B3" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729295</v>
+        <v>729062</v>
       </c>
       <c r="R3" t="n">
-        <v>7389011</v>
+        <v>7389313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119541278</v>
+        <v>119541197</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729224</v>
+        <v>729154</v>
       </c>
       <c r="R4" t="n">
-        <v>7389317</v>
+        <v>7389019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119541279</v>
+        <v>119541212</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>86412</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729062</v>
+        <v>729295</v>
       </c>
       <c r="R5" t="n">
-        <v>7389313</v>
+        <v>7389011</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119541208</v>
+        <v>119541206</v>
       </c>
       <c r="B12" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729190</v>
+        <v>728984</v>
       </c>
       <c r="R12" t="n">
-        <v>7389286</v>
+        <v>7389224</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,7 +1779,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119541206</v>
+        <v>119541208</v>
       </c>
       <c r="B14" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1940,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>728984</v>
+        <v>729190</v>
       </c>
       <c r="R14" t="n">
-        <v>7389224</v>
+        <v>7389286</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,6 +1983,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119541291</v>
+        <v>119541243</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729014</v>
+        <v>729279</v>
       </c>
       <c r="R23" t="n">
-        <v>7389291</v>
+        <v>7388997</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119541243</v>
+        <v>119541236</v>
       </c>
       <c r="B24" t="n">
-        <v>57326</v>
+        <v>91884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729279</v>
+        <v>729034</v>
       </c>
       <c r="R24" t="n">
-        <v>7388997</v>
+        <v>7389252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119541236</v>
+        <v>119541291</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729034</v>
+        <v>729014</v>
       </c>
       <c r="R25" t="n">
-        <v>7389252</v>
+        <v>7389291</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4354,10 +4354,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119541264</v>
+        <v>119541205</v>
       </c>
       <c r="B38" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>729223</v>
+        <v>729131</v>
       </c>
       <c r="R38" t="n">
-        <v>7389241</v>
+        <v>7389195</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119541299</v>
+        <v>119541192</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>88153</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4468,25 +4468,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729302</v>
+        <v>729192</v>
       </c>
       <c r="R39" t="n">
-        <v>7389005</v>
+        <v>7389302</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119541283</v>
+        <v>119541257</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4574,21 +4574,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729151</v>
+        <v>729026</v>
       </c>
       <c r="R40" t="n">
-        <v>7389249</v>
+        <v>7389281</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119541205</v>
+        <v>119541264</v>
       </c>
       <c r="B41" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4676,21 +4676,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729131</v>
+        <v>729223</v>
       </c>
       <c r="R41" t="n">
-        <v>7389195</v>
+        <v>7389241</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4762,10 +4762,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119541192</v>
+        <v>119541299</v>
       </c>
       <c r="B42" t="n">
-        <v>88153</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4774,25 +4774,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729192</v>
+        <v>729302</v>
       </c>
       <c r="R42" t="n">
-        <v>7389302</v>
+        <v>7389005</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119541257</v>
+        <v>119541283</v>
       </c>
       <c r="B43" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4880,21 +4880,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729026</v>
+        <v>729151</v>
       </c>
       <c r="R43" t="n">
-        <v>7389281</v>
+        <v>7389249</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119541216</v>
+        <v>119541253</v>
       </c>
       <c r="B46" t="n">
-        <v>86412</v>
+        <v>96868</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5183,25 +5183,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3690</v>
+        <v>221941</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>729027</v>
+        <v>729273</v>
       </c>
       <c r="R46" t="n">
-        <v>7389265</v>
+        <v>7389025</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5255,7 +5255,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5274,10 +5273,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119541204</v>
+        <v>119541240</v>
       </c>
       <c r="B47" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5290,21 +5289,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5314,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729234</v>
+        <v>729204</v>
       </c>
       <c r="R47" t="n">
-        <v>7389233</v>
+        <v>7389007</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5376,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119541240</v>
+        <v>119541216</v>
       </c>
       <c r="B48" t="n">
-        <v>91884</v>
+        <v>86412</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5392,21 +5391,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>3690</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5416,10 +5415,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729204</v>
+        <v>729027</v>
       </c>
       <c r="R48" t="n">
-        <v>7389007</v>
+        <v>7389265</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5460,6 +5459,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119541253</v>
+        <v>119541204</v>
       </c>
       <c r="B49" t="n">
-        <v>96868</v>
+        <v>79144</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5490,25 +5490,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729273</v>
+        <v>729234</v>
       </c>
       <c r="R49" t="n">
-        <v>7389025</v>
+        <v>7389233</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119541194</v>
+        <v>119541258</v>
       </c>
       <c r="B50" t="n">
-        <v>87406</v>
+        <v>96868</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4412</v>
+        <v>221941</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729247</v>
+        <v>729030</v>
       </c>
       <c r="R50" t="n">
-        <v>7389213</v>
+        <v>7389117</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119541198</v>
+        <v>119541194</v>
       </c>
       <c r="B51" t="n">
         <v>87406</v>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729161</v>
+        <v>729247</v>
       </c>
       <c r="R51" t="n">
-        <v>7389019</v>
+        <v>7389213</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119541268</v>
+        <v>119541198</v>
       </c>
       <c r="B52" t="n">
-        <v>78262</v>
+        <v>87406</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5800,21 +5800,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729230</v>
+        <v>729161</v>
       </c>
       <c r="R52" t="n">
-        <v>7389247</v>
+        <v>7389019</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5862,18 +5862,12 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5892,10 +5886,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119541258</v>
+        <v>119541268</v>
       </c>
       <c r="B53" t="n">
-        <v>96868</v>
+        <v>78262</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5904,25 +5898,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5932,10 +5926,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729030</v>
+        <v>729230</v>
       </c>
       <c r="R53" t="n">
-        <v>7389117</v>
+        <v>7389247</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5970,12 +5964,18 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6402,10 +6402,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119541265</v>
+        <v>119541298</v>
       </c>
       <c r="B58" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6414,25 +6414,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729145</v>
+        <v>729271</v>
       </c>
       <c r="R58" t="n">
-        <v>7389330</v>
+        <v>7388970</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6504,10 +6504,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119541207</v>
+        <v>119541286</v>
       </c>
       <c r="B59" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6516,25 +6516,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>729102</v>
+        <v>729172</v>
       </c>
       <c r="R59" t="n">
-        <v>7389109</v>
+        <v>7389192</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6606,10 +6606,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119541235</v>
+        <v>119541287</v>
       </c>
       <c r="B60" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6618,25 +6618,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>729331</v>
+        <v>729086</v>
       </c>
       <c r="R60" t="n">
-        <v>7389160</v>
+        <v>7389202</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6708,10 +6708,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119541298</v>
+        <v>119541207</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6720,25 +6720,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>729271</v>
+        <v>729102</v>
       </c>
       <c r="R61" t="n">
-        <v>7388970</v>
+        <v>7389109</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6810,10 +6810,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119541286</v>
+        <v>119541265</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6822,25 +6822,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6850,10 +6850,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>729172</v>
+        <v>729145</v>
       </c>
       <c r="R62" t="n">
-        <v>7389192</v>
+        <v>7389330</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6912,10 +6912,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119541287</v>
+        <v>119541235</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6924,25 +6924,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>729086</v>
+        <v>729331</v>
       </c>
       <c r="R63" t="n">
-        <v>7389202</v>
+        <v>7389160</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8749,7 +8749,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119541284</v>
+        <v>119541282</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729164</v>
+        <v>729120</v>
       </c>
       <c r="R81" t="n">
-        <v>7389239</v>
+        <v>7389280</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8851,10 +8851,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119541266</v>
+        <v>119541296</v>
       </c>
       <c r="B82" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8863,25 +8863,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729131</v>
+        <v>729148</v>
       </c>
       <c r="R82" t="n">
-        <v>7389195</v>
+        <v>7389020</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8953,7 +8953,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119541282</v>
+        <v>119541284</v>
       </c>
       <c r="B83" t="n">
         <v>91840</v>
@@ -8993,10 +8993,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>729120</v>
+        <v>729164</v>
       </c>
       <c r="R83" t="n">
-        <v>7389280</v>
+        <v>7389239</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9055,10 +9055,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119541296</v>
+        <v>119541203</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9067,25 +9067,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9095,10 +9095,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>729148</v>
+        <v>729244</v>
       </c>
       <c r="R84" t="n">
-        <v>7389020</v>
+        <v>7389219</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9157,10 +9157,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119541256</v>
+        <v>119541266</v>
       </c>
       <c r="B85" t="n">
-        <v>96868</v>
+        <v>78262</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9169,25 +9169,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9197,10 +9197,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>729155</v>
+        <v>729131</v>
       </c>
       <c r="R85" t="n">
-        <v>7389249</v>
+        <v>7389195</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119541267</v>
+        <v>119541256</v>
       </c>
       <c r="B86" t="n">
-        <v>78263</v>
+        <v>96868</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9271,25 +9271,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9299,10 +9299,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>729230</v>
+        <v>729155</v>
       </c>
       <c r="R86" t="n">
-        <v>7389231</v>
+        <v>7389249</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9337,18 +9337,12 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9367,10 +9361,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119541203</v>
+        <v>119541267</v>
       </c>
       <c r="B87" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9383,21 +9377,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9407,10 +9401,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>729244</v>
+        <v>729230</v>
       </c>
       <c r="R87" t="n">
-        <v>7389219</v>
+        <v>7389231</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9445,12 +9439,18 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34593-2024 artfynd.xlsx
+++ b/artfynd/A 34593-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119541231</v>
+        <v>119541293</v>
       </c>
       <c r="B6" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729190</v>
+        <v>728966</v>
       </c>
       <c r="R6" t="n">
-        <v>7389184</v>
+        <v>7389240</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119541262</v>
+        <v>119541202</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729346</v>
+        <v>729249</v>
       </c>
       <c r="R7" t="n">
-        <v>7389145</v>
+        <v>7389192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119541293</v>
+        <v>119541231</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>728966</v>
+        <v>729190</v>
       </c>
       <c r="R8" t="n">
-        <v>7389240</v>
+        <v>7389184</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119541202</v>
+        <v>119541262</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729249</v>
+        <v>729346</v>
       </c>
       <c r="R9" t="n">
-        <v>7389192</v>
+        <v>7389145</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119541253</v>
+        <v>119541216</v>
       </c>
       <c r="B46" t="n">
-        <v>96868</v>
+        <v>86412</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5183,25 +5183,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>3690</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>729273</v>
+        <v>729027</v>
       </c>
       <c r="R46" t="n">
-        <v>7389025</v>
+        <v>7389265</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5255,6 +5255,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5273,10 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119541240</v>
+        <v>119541204</v>
       </c>
       <c r="B47" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5289,21 +5290,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5313,10 +5314,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729204</v>
+        <v>729234</v>
       </c>
       <c r="R47" t="n">
-        <v>7389007</v>
+        <v>7389233</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,10 +5376,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119541216</v>
+        <v>119541240</v>
       </c>
       <c r="B48" t="n">
-        <v>86412</v>
+        <v>91884</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5391,21 +5392,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3690</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5415,10 +5416,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729027</v>
+        <v>729204</v>
       </c>
       <c r="R48" t="n">
-        <v>7389265</v>
+        <v>7389007</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5459,7 +5460,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119541204</v>
+        <v>119541253</v>
       </c>
       <c r="B49" t="n">
-        <v>79144</v>
+        <v>96868</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5490,25 +5490,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729234</v>
+        <v>729273</v>
       </c>
       <c r="R49" t="n">
-        <v>7389233</v>
+        <v>7389025</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119541258</v>
+        <v>119541194</v>
       </c>
       <c r="B50" t="n">
-        <v>96868</v>
+        <v>87406</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221941</v>
+        <v>4412</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729030</v>
+        <v>729247</v>
       </c>
       <c r="R50" t="n">
-        <v>7389117</v>
+        <v>7389213</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119541194</v>
+        <v>119541198</v>
       </c>
       <c r="B51" t="n">
         <v>87406</v>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729247</v>
+        <v>729161</v>
       </c>
       <c r="R51" t="n">
-        <v>7389213</v>
+        <v>7389019</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119541198</v>
+        <v>119541268</v>
       </c>
       <c r="B52" t="n">
-        <v>87406</v>
+        <v>78262</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5800,21 +5800,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4412</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729161</v>
+        <v>729230</v>
       </c>
       <c r="R52" t="n">
-        <v>7389019</v>
+        <v>7389247</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5862,12 +5862,18 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5886,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119541268</v>
+        <v>119541258</v>
       </c>
       <c r="B53" t="n">
-        <v>78262</v>
+        <v>96868</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5898,25 +5904,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5926,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729230</v>
+        <v>729030</v>
       </c>
       <c r="R53" t="n">
-        <v>7389247</v>
+        <v>7389117</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5964,18 +5970,12 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7932,10 +7932,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119541193</v>
+        <v>119541247</v>
       </c>
       <c r="B73" t="n">
-        <v>88153</v>
+        <v>91856</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7948,21 +7948,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4962</v>
+        <v>2059</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7972,10 +7972,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>729066</v>
+        <v>729128</v>
       </c>
       <c r="R73" t="n">
-        <v>7389193</v>
+        <v>7389194</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8034,10 +8034,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119541195</v>
+        <v>119541193</v>
       </c>
       <c r="B74" t="n">
-        <v>87406</v>
+        <v>88153</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8050,21 +8050,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4412</v>
+        <v>4962</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8074,10 +8074,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>729146</v>
+        <v>729066</v>
       </c>
       <c r="R74" t="n">
-        <v>7389045</v>
+        <v>7389193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8136,10 +8136,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119541247</v>
+        <v>119541195</v>
       </c>
       <c r="B75" t="n">
-        <v>91856</v>
+        <v>87406</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8152,21 +8152,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2059</v>
+        <v>4412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8176,10 +8176,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729128</v>
+        <v>729146</v>
       </c>
       <c r="R75" t="n">
-        <v>7389194</v>
+        <v>7389045</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 34593-2024 artfynd.xlsx
+++ b/artfynd/A 34593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119541278</v>
+        <v>119541234</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729224</v>
+        <v>729248</v>
       </c>
       <c r="R2" t="n">
-        <v>7389317</v>
+        <v>7389111</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119541279</v>
+        <v>119541271</v>
       </c>
       <c r="B3" t="n">
         <v>91840</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729062</v>
+        <v>729245</v>
       </c>
       <c r="R3" t="n">
-        <v>7389313</v>
+        <v>7389062</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119541197</v>
+        <v>119541191</v>
       </c>
       <c r="B4" t="n">
         <v>87406</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729154</v>
+        <v>729250</v>
       </c>
       <c r="R4" t="n">
-        <v>7389019</v>
+        <v>7389202</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119541212</v>
+        <v>119541288</v>
       </c>
       <c r="B5" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729295</v>
+        <v>729066</v>
       </c>
       <c r="R5" t="n">
-        <v>7389011</v>
+        <v>7389193</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119541293</v>
+        <v>119541231</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>728966</v>
+        <v>729190</v>
       </c>
       <c r="R6" t="n">
-        <v>7389240</v>
+        <v>7389184</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119541202</v>
+        <v>119541192</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>88153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729249</v>
+        <v>729192</v>
       </c>
       <c r="R7" t="n">
-        <v>7389192</v>
+        <v>7389302</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119541231</v>
+        <v>119541263</v>
       </c>
       <c r="B8" t="n">
-        <v>91463</v>
+        <v>78262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4745</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729190</v>
+        <v>729248</v>
       </c>
       <c r="R8" t="n">
-        <v>7389184</v>
+        <v>7389196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119541262</v>
+        <v>119541258</v>
       </c>
       <c r="B9" t="n">
-        <v>78262</v>
+        <v>96868</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729346</v>
+        <v>729030</v>
       </c>
       <c r="R9" t="n">
-        <v>7389145</v>
+        <v>7389117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119541239</v>
+        <v>119541236</v>
       </c>
       <c r="B10" t="n">
         <v>91884</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729192</v>
+        <v>729034</v>
       </c>
       <c r="R10" t="n">
-        <v>7389008</v>
+        <v>7389252</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119541199</v>
+        <v>119541204</v>
       </c>
       <c r="B11" t="n">
-        <v>87406</v>
+        <v>79144</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4412</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729173</v>
+        <v>729234</v>
       </c>
       <c r="R11" t="n">
-        <v>7389021</v>
+        <v>7389233</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119541206</v>
+        <v>119541245</v>
       </c>
       <c r="B12" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>728984</v>
+        <v>729274</v>
       </c>
       <c r="R12" t="n">
-        <v>7389224</v>
+        <v>7389205</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119541220</v>
+        <v>119541299</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729097</v>
+        <v>729302</v>
       </c>
       <c r="R13" t="n">
-        <v>7389119</v>
+        <v>7389005</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119541208</v>
+        <v>119541257</v>
       </c>
       <c r="B14" t="n">
-        <v>79115</v>
+        <v>96868</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729190</v>
+        <v>729026</v>
       </c>
       <c r="R14" t="n">
-        <v>7389286</v>
+        <v>7389281</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,7 +1983,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2002,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119541213</v>
+        <v>119541250</v>
       </c>
       <c r="B15" t="n">
-        <v>86412</v>
+        <v>91856</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2042,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729100</v>
+        <v>729191</v>
       </c>
       <c r="R15" t="n">
-        <v>7389150</v>
+        <v>7389198</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119541285</v>
+        <v>119541238</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2116,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729190</v>
+        <v>729030</v>
       </c>
       <c r="R16" t="n">
-        <v>7389208</v>
+        <v>7389117</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119541289</v>
+        <v>119541200</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2218,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2246,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729031</v>
+        <v>729251</v>
       </c>
       <c r="R17" t="n">
-        <v>7389263</v>
+        <v>7389063</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119541292</v>
+        <v>119541298</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2348,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>728973</v>
+        <v>729271</v>
       </c>
       <c r="R18" t="n">
-        <v>7389250</v>
+        <v>7388970</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119541297</v>
+        <v>119541285</v>
       </c>
       <c r="B19" t="n">
         <v>91840</v>
@@ -2450,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729203</v>
+        <v>729190</v>
       </c>
       <c r="R19" t="n">
-        <v>7389019</v>
+        <v>7389208</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119541238</v>
+        <v>119541296</v>
       </c>
       <c r="B20" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2524,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>729030</v>
+        <v>729148</v>
       </c>
       <c r="R20" t="n">
-        <v>7389117</v>
+        <v>7389020</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119541260</v>
+        <v>119541243</v>
       </c>
       <c r="B21" t="n">
-        <v>80483</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,37 +2629,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Själláriemgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729227</v>
+        <v>729279</v>
       </c>
       <c r="R21" t="n">
-        <v>7389252</v>
+        <v>7388997</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,12 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2701,7 +2697,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119541263</v>
+        <v>119541195</v>
       </c>
       <c r="B22" t="n">
-        <v>78262</v>
+        <v>87406</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729248</v>
+        <v>729146</v>
       </c>
       <c r="R22" t="n">
-        <v>7389196</v>
+        <v>7389045</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119541243</v>
+        <v>119541199</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>87406</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729279</v>
+        <v>729173</v>
       </c>
       <c r="R23" t="n">
-        <v>7388997</v>
+        <v>7389021</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119541236</v>
+        <v>119541215</v>
       </c>
       <c r="B24" t="n">
-        <v>91884</v>
+        <v>86412</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>3690</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729034</v>
+        <v>729329</v>
       </c>
       <c r="R24" t="n">
-        <v>7389252</v>
+        <v>7389121</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3008,6 +3003,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3026,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119541291</v>
+        <v>119541252</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>96862</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3038,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729014</v>
+        <v>729140</v>
       </c>
       <c r="R25" t="n">
-        <v>7389291</v>
+        <v>7389338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3124,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119541245</v>
+        <v>119541295</v>
       </c>
       <c r="B26" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3136,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729274</v>
+        <v>729099</v>
       </c>
       <c r="R26" t="n">
-        <v>7389205</v>
+        <v>7389146</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,7 +3226,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119541246</v>
+        <v>119541244</v>
       </c>
       <c r="B27" t="n">
         <v>91856</v>
@@ -3270,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729182</v>
+        <v>729255</v>
       </c>
       <c r="R27" t="n">
-        <v>7389188</v>
+        <v>7389071</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3328,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119541217</v>
+        <v>119541237</v>
       </c>
       <c r="B28" t="n">
-        <v>86412</v>
+        <v>91884</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,21 +3344,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3690</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729203</v>
+        <v>729011</v>
       </c>
       <c r="R28" t="n">
-        <v>7389017</v>
+        <v>7389279</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,7 +3412,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3435,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119541234</v>
+        <v>119541276</v>
       </c>
       <c r="B29" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3447,25 +3442,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3475,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729248</v>
+        <v>729228</v>
       </c>
       <c r="R29" t="n">
-        <v>7389111</v>
+        <v>7389283</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,10 +3532,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119541191</v>
+        <v>119541279</v>
       </c>
       <c r="B30" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3549,25 +3544,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3577,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>729250</v>
+        <v>729062</v>
       </c>
       <c r="R30" t="n">
-        <v>7389202</v>
+        <v>7389313</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3639,7 +3634,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119541271</v>
+        <v>119541292</v>
       </c>
       <c r="B31" t="n">
         <v>91840</v>
@@ -3679,10 +3674,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>729245</v>
+        <v>728973</v>
       </c>
       <c r="R31" t="n">
-        <v>7389062</v>
+        <v>7389250</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3741,10 +3736,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119541215</v>
+        <v>119541251</v>
       </c>
       <c r="B32" t="n">
-        <v>86412</v>
+        <v>91852</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3753,25 +3748,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3781,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>729329</v>
+        <v>729030</v>
       </c>
       <c r="R32" t="n">
-        <v>7389121</v>
+        <v>7389117</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3825,7 +3820,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3844,7 +3838,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119541276</v>
+        <v>119541297</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -3884,10 +3878,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>729228</v>
+        <v>729203</v>
       </c>
       <c r="R33" t="n">
-        <v>7389283</v>
+        <v>7389019</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119541273</v>
+        <v>119541206</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3958,25 +3952,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3986,10 +3980,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>729321</v>
+        <v>728984</v>
       </c>
       <c r="R34" t="n">
-        <v>7389192</v>
+        <v>7389224</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4048,10 +4042,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119541244</v>
+        <v>119541253</v>
       </c>
       <c r="B35" t="n">
-        <v>91856</v>
+        <v>96868</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4060,25 +4054,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4088,10 +4082,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729255</v>
+        <v>729273</v>
       </c>
       <c r="R35" t="n">
-        <v>7389071</v>
+        <v>7389025</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4150,10 +4144,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119541232</v>
+        <v>119541209</v>
       </c>
       <c r="B36" t="n">
-        <v>91883</v>
+        <v>79115</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4166,21 +4160,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5448</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4190,10 +4184,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729027</v>
+        <v>729275</v>
       </c>
       <c r="R36" t="n">
-        <v>7389271</v>
+        <v>7389001</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4234,6 +4228,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4252,7 +4247,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119541255</v>
+        <v>119541256</v>
       </c>
       <c r="B37" t="n">
         <v>96868</v>
@@ -4292,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>729136</v>
+        <v>729155</v>
       </c>
       <c r="R37" t="n">
-        <v>7389254</v>
+        <v>7389249</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4354,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119541205</v>
+        <v>119541194</v>
       </c>
       <c r="B38" t="n">
-        <v>79144</v>
+        <v>87406</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4370,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>729131</v>
+        <v>729247</v>
       </c>
       <c r="R38" t="n">
-        <v>7389195</v>
+        <v>7389213</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119541192</v>
+        <v>119541203</v>
       </c>
       <c r="B39" t="n">
-        <v>88153</v>
+        <v>79144</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4472,21 +4467,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4496,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729192</v>
+        <v>729244</v>
       </c>
       <c r="R39" t="n">
-        <v>7389302</v>
+        <v>7389219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4558,10 +4553,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119541257</v>
+        <v>119541291</v>
       </c>
       <c r="B40" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4574,21 +4569,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4598,10 +4593,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729026</v>
+        <v>729014</v>
       </c>
       <c r="R40" t="n">
-        <v>7389281</v>
+        <v>7389291</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4660,10 +4655,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119541264</v>
+        <v>119541220</v>
       </c>
       <c r="B41" t="n">
-        <v>78262</v>
+        <v>57463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4676,21 +4671,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4700,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729223</v>
+        <v>729097</v>
       </c>
       <c r="R41" t="n">
-        <v>7389241</v>
+        <v>7389119</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4762,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119541299</v>
+        <v>119541255</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4778,21 +4773,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4802,10 +4797,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729302</v>
+        <v>729136</v>
       </c>
       <c r="R42" t="n">
-        <v>7389005</v>
+        <v>7389254</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4864,10 +4859,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119541283</v>
+        <v>119541197</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4876,25 +4871,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4904,10 +4899,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729151</v>
+        <v>729154</v>
       </c>
       <c r="R43" t="n">
-        <v>7389249</v>
+        <v>7389019</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4966,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119541209</v>
+        <v>119541207</v>
       </c>
       <c r="B44" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4982,21 +4977,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5006,10 +5001,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>729275</v>
+        <v>729102</v>
       </c>
       <c r="R44" t="n">
-        <v>7389001</v>
+        <v>7389109</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5050,7 +5045,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5069,10 +5063,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119541251</v>
+        <v>119541278</v>
       </c>
       <c r="B45" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5079,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5103,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>729030</v>
+        <v>729224</v>
       </c>
       <c r="R45" t="n">
-        <v>7389117</v>
+        <v>7389317</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5171,10 +5165,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119541216</v>
+        <v>119541287</v>
       </c>
       <c r="B46" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5183,25 +5177,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5205,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>729027</v>
+        <v>729086</v>
       </c>
       <c r="R46" t="n">
-        <v>7389265</v>
+        <v>7389202</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5255,7 +5249,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5274,10 +5267,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119541204</v>
+        <v>119541208</v>
       </c>
       <c r="B47" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5290,21 +5283,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5314,10 +5307,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729234</v>
+        <v>729190</v>
       </c>
       <c r="R47" t="n">
-        <v>7389233</v>
+        <v>7389286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5358,6 +5351,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5376,10 +5370,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119541240</v>
+        <v>119541267</v>
       </c>
       <c r="B48" t="n">
-        <v>91884</v>
+        <v>78263</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5392,21 +5386,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5416,10 +5410,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729204</v>
+        <v>729230</v>
       </c>
       <c r="R48" t="n">
-        <v>7389007</v>
+        <v>7389231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5454,12 +5448,18 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119541253</v>
+        <v>119541241</v>
       </c>
       <c r="B49" t="n">
-        <v>96868</v>
+        <v>57326</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5490,25 +5490,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729273</v>
+        <v>729213</v>
       </c>
       <c r="R49" t="n">
-        <v>7389025</v>
+        <v>7389307</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119541194</v>
+        <v>119541219</v>
       </c>
       <c r="B50" t="n">
-        <v>87406</v>
+        <v>86412</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5596,21 +5596,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4412</v>
+        <v>3690</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729247</v>
+        <v>729031</v>
       </c>
       <c r="R50" t="n">
-        <v>7389213</v>
+        <v>7389139</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5682,10 +5682,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119541198</v>
+        <v>119541266</v>
       </c>
       <c r="B51" t="n">
-        <v>87406</v>
+        <v>78262</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5698,21 +5698,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4412</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729161</v>
+        <v>729131</v>
       </c>
       <c r="R51" t="n">
-        <v>7389019</v>
+        <v>7389195</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119541268</v>
+        <v>119541205</v>
       </c>
       <c r="B52" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5800,21 +5800,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729230</v>
+        <v>729131</v>
       </c>
       <c r="R52" t="n">
-        <v>7389247</v>
+        <v>7389195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5862,18 +5862,12 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5892,10 +5886,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119541258</v>
+        <v>119541290</v>
       </c>
       <c r="B53" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5908,21 +5902,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5932,10 +5926,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729030</v>
+        <v>729022</v>
       </c>
       <c r="R53" t="n">
-        <v>7389117</v>
+        <v>7389283</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5994,10 +5988,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119541219</v>
+        <v>119541300</v>
       </c>
       <c r="B54" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6006,25 +6000,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6034,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729031</v>
+        <v>729015</v>
       </c>
       <c r="R54" t="n">
-        <v>7389139</v>
+        <v>7389279</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6078,6 +6072,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6096,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119541275</v>
+        <v>119541246</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6108,25 +6103,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729277</v>
+        <v>729182</v>
       </c>
       <c r="R55" t="n">
-        <v>7389208</v>
+        <v>7389188</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6198,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119541237</v>
+        <v>119541213</v>
       </c>
       <c r="B56" t="n">
-        <v>91884</v>
+        <v>86412</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6214,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5449</v>
+        <v>3690</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6238,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729011</v>
+        <v>729100</v>
       </c>
       <c r="R56" t="n">
-        <v>7389279</v>
+        <v>7389150</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6300,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119541252</v>
+        <v>119541235</v>
       </c>
       <c r="B57" t="n">
-        <v>96862</v>
+        <v>91884</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6312,25 +6307,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6340,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729140</v>
+        <v>729331</v>
       </c>
       <c r="R57" t="n">
-        <v>7389338</v>
+        <v>7389160</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6402,10 +6397,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119541298</v>
+        <v>119541239</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6414,25 +6409,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6442,10 +6437,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729271</v>
+        <v>729192</v>
       </c>
       <c r="R58" t="n">
-        <v>7388970</v>
+        <v>7389008</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6504,10 +6499,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119541286</v>
+        <v>119541260</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>80483</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6516,38 +6511,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Själláriemgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>729172</v>
+        <v>729227</v>
       </c>
       <c r="R59" t="n">
-        <v>7389192</v>
+        <v>7389252</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6574,12 +6572,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6588,6 +6586,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6606,10 +6605,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119541287</v>
+        <v>119541201</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6618,25 +6617,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6646,10 +6645,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>729086</v>
+        <v>729236</v>
       </c>
       <c r="R60" t="n">
-        <v>7389202</v>
+        <v>7389109</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6708,10 +6707,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119541207</v>
+        <v>119541232</v>
       </c>
       <c r="B61" t="n">
-        <v>79144</v>
+        <v>91883</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6724,21 +6723,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6748,10 +6747,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>729102</v>
+        <v>729027</v>
       </c>
       <c r="R61" t="n">
-        <v>7389109</v>
+        <v>7389271</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6810,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119541265</v>
+        <v>119541248</v>
       </c>
       <c r="B62" t="n">
-        <v>78262</v>
+        <v>91856</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6826,21 +6825,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6850,10 +6849,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>729145</v>
+        <v>729004</v>
       </c>
       <c r="R62" t="n">
-        <v>7389330</v>
+        <v>7389281</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6912,10 +6911,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119541235</v>
+        <v>119541249</v>
       </c>
       <c r="B63" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6928,21 +6927,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6951,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>729331</v>
+        <v>728969</v>
       </c>
       <c r="R63" t="n">
-        <v>7389160</v>
+        <v>7389214</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,7 +7013,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119541290</v>
+        <v>119541275</v>
       </c>
       <c r="B64" t="n">
         <v>91840</v>
@@ -7054,10 +7053,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>729022</v>
+        <v>729277</v>
       </c>
       <c r="R64" t="n">
-        <v>7389283</v>
+        <v>7389208</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7218,10 +7217,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119541200</v>
+        <v>119541217</v>
       </c>
       <c r="B66" t="n">
-        <v>79144</v>
+        <v>86412</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7234,21 +7233,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7258,10 +7257,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>729251</v>
+        <v>729203</v>
       </c>
       <c r="R66" t="n">
-        <v>7389063</v>
+        <v>7389017</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7302,6 +7301,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7320,10 +7320,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119541196</v>
+        <v>119541193</v>
       </c>
       <c r="B67" t="n">
-        <v>87406</v>
+        <v>88153</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7336,21 +7336,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4412</v>
+        <v>4962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>729151</v>
+        <v>729066</v>
       </c>
       <c r="R67" t="n">
-        <v>7389037</v>
+        <v>7389193</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7422,10 +7422,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119541274</v>
+        <v>119541240</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7434,25 +7434,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>729292</v>
+        <v>729204</v>
       </c>
       <c r="R68" t="n">
-        <v>7389205</v>
+        <v>7389007</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7524,10 +7524,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119541295</v>
+        <v>119541264</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7536,25 +7536,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>729099</v>
+        <v>729223</v>
       </c>
       <c r="R69" t="n">
-        <v>7389146</v>
+        <v>7389241</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7626,10 +7626,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119541281</v>
+        <v>119541268</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7638,25 +7638,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>729079</v>
+        <v>729230</v>
       </c>
       <c r="R70" t="n">
-        <v>7389314</v>
+        <v>7389247</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7704,12 +7704,18 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7728,7 +7734,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119541288</v>
+        <v>119541289</v>
       </c>
       <c r="B71" t="n">
         <v>91840</v>
@@ -7768,10 +7774,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>729066</v>
+        <v>729031</v>
       </c>
       <c r="R71" t="n">
-        <v>7389193</v>
+        <v>7389263</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7830,10 +7836,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119541201</v>
+        <v>119541247</v>
       </c>
       <c r="B72" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7846,21 +7852,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7870,10 +7876,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>729236</v>
+        <v>729128</v>
       </c>
       <c r="R72" t="n">
-        <v>7389109</v>
+        <v>7389194</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7932,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119541247</v>
+        <v>119541274</v>
       </c>
       <c r="B73" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7944,25 +7950,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7972,10 +7978,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>729128</v>
+        <v>729292</v>
       </c>
       <c r="R73" t="n">
-        <v>7389194</v>
+        <v>7389205</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8034,10 +8040,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119541193</v>
+        <v>119541286</v>
       </c>
       <c r="B74" t="n">
-        <v>88153</v>
+        <v>91840</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8046,25 +8052,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8074,10 +8080,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>729066</v>
+        <v>729172</v>
       </c>
       <c r="R74" t="n">
-        <v>7389193</v>
+        <v>7389192</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8136,10 +8142,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119541195</v>
+        <v>119541282</v>
       </c>
       <c r="B75" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8148,25 +8154,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8176,10 +8182,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729146</v>
+        <v>729120</v>
       </c>
       <c r="R75" t="n">
-        <v>7389045</v>
+        <v>7389280</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8238,7 +8244,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119541300</v>
+        <v>119541273</v>
       </c>
       <c r="B76" t="n">
         <v>91840</v>
@@ -8278,10 +8284,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>729015</v>
+        <v>729321</v>
       </c>
       <c r="R76" t="n">
-        <v>7389279</v>
+        <v>7389192</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8322,7 +8328,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8341,10 +8346,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119541250</v>
+        <v>119541284</v>
       </c>
       <c r="B77" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8353,25 +8358,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8381,10 +8386,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>729191</v>
+        <v>729164</v>
       </c>
       <c r="R77" t="n">
-        <v>7389198</v>
+        <v>7389239</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8443,10 +8448,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119541248</v>
+        <v>119541202</v>
       </c>
       <c r="B78" t="n">
-        <v>91856</v>
+        <v>79144</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8459,21 +8464,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8483,10 +8488,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>729004</v>
+        <v>729249</v>
       </c>
       <c r="R78" t="n">
-        <v>7389281</v>
+        <v>7389192</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8545,10 +8550,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119541249</v>
+        <v>119541212</v>
       </c>
       <c r="B79" t="n">
-        <v>91856</v>
+        <v>86412</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8561,21 +8566,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>3690</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8585,10 +8590,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>728969</v>
+        <v>729295</v>
       </c>
       <c r="R79" t="n">
-        <v>7389214</v>
+        <v>7389011</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8647,10 +8652,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119541241</v>
+        <v>119541196</v>
       </c>
       <c r="B80" t="n">
-        <v>57326</v>
+        <v>87406</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8663,21 +8668,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8687,10 +8692,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729213</v>
+        <v>729151</v>
       </c>
       <c r="R80" t="n">
-        <v>7389307</v>
+        <v>7389037</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8749,10 +8754,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119541282</v>
+        <v>119541265</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8761,25 +8766,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8789,10 +8794,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729120</v>
+        <v>729145</v>
       </c>
       <c r="R81" t="n">
-        <v>7389280</v>
+        <v>7389330</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8851,7 +8856,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119541296</v>
+        <v>119541281</v>
       </c>
       <c r="B82" t="n">
         <v>91840</v>
@@ -8891,10 +8896,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729148</v>
+        <v>729079</v>
       </c>
       <c r="R82" t="n">
-        <v>7389020</v>
+        <v>7389314</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8953,7 +8958,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119541284</v>
+        <v>119541293</v>
       </c>
       <c r="B83" t="n">
         <v>91840</v>
@@ -8993,10 +8998,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>729164</v>
+        <v>728966</v>
       </c>
       <c r="R83" t="n">
-        <v>7389239</v>
+        <v>7389240</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9055,10 +9060,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119541203</v>
+        <v>119541216</v>
       </c>
       <c r="B84" t="n">
-        <v>79144</v>
+        <v>86412</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9071,21 +9076,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9095,10 +9100,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>729244</v>
+        <v>729027</v>
       </c>
       <c r="R84" t="n">
-        <v>7389219</v>
+        <v>7389265</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9139,6 +9144,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9157,10 +9163,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119541266</v>
+        <v>119541283</v>
       </c>
       <c r="B85" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9169,25 +9175,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9197,10 +9203,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>729131</v>
+        <v>729151</v>
       </c>
       <c r="R85" t="n">
-        <v>7389195</v>
+        <v>7389249</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9259,10 +9265,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119541256</v>
+        <v>119541262</v>
       </c>
       <c r="B86" t="n">
-        <v>96868</v>
+        <v>78262</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9271,25 +9277,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9299,10 +9305,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>729155</v>
+        <v>729346</v>
       </c>
       <c r="R86" t="n">
-        <v>7389249</v>
+        <v>7389145</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9361,10 +9367,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119541267</v>
+        <v>119541198</v>
       </c>
       <c r="B87" t="n">
-        <v>78263</v>
+        <v>87406</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9377,21 +9383,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>4412</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9401,10 +9407,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>729230</v>
+        <v>729161</v>
       </c>
       <c r="R87" t="n">
-        <v>7389231</v>
+        <v>7389019</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9439,18 +9445,12 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34593-2024 artfynd.xlsx
+++ b/artfynd/A 34593-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119541258</v>
+        <v>119541236</v>
       </c>
       <c r="B9" t="n">
-        <v>96868</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729030</v>
+        <v>729034</v>
       </c>
       <c r="R9" t="n">
-        <v>7389117</v>
+        <v>7389252</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119541236</v>
+        <v>119541204</v>
       </c>
       <c r="B10" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729034</v>
+        <v>729234</v>
       </c>
       <c r="R10" t="n">
-        <v>7389252</v>
+        <v>7389233</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119541204</v>
+        <v>119541299</v>
       </c>
       <c r="B11" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729234</v>
+        <v>729302</v>
       </c>
       <c r="R11" t="n">
-        <v>7389233</v>
+        <v>7389005</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119541299</v>
+        <v>119541258</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729302</v>
+        <v>729030</v>
       </c>
       <c r="R13" t="n">
-        <v>7389005</v>
+        <v>7389117</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119541257</v>
+        <v>119541298</v>
       </c>
       <c r="B14" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729026</v>
+        <v>729271</v>
       </c>
       <c r="R14" t="n">
-        <v>7389281</v>
+        <v>7388970</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119541250</v>
+        <v>119541285</v>
       </c>
       <c r="B15" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729191</v>
+        <v>729190</v>
       </c>
       <c r="R15" t="n">
-        <v>7389198</v>
+        <v>7389208</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119541238</v>
+        <v>119541296</v>
       </c>
       <c r="B16" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729030</v>
+        <v>729148</v>
       </c>
       <c r="R16" t="n">
-        <v>7389117</v>
+        <v>7389020</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119541200</v>
+        <v>119541250</v>
       </c>
       <c r="B17" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729251</v>
+        <v>729191</v>
       </c>
       <c r="R17" t="n">
-        <v>7389063</v>
+        <v>7389198</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119541298</v>
+        <v>119541238</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729271</v>
+        <v>729030</v>
       </c>
       <c r="R18" t="n">
-        <v>7388970</v>
+        <v>7389117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119541285</v>
+        <v>119541200</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729190</v>
+        <v>729251</v>
       </c>
       <c r="R19" t="n">
-        <v>7389208</v>
+        <v>7389063</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119541296</v>
+        <v>119541243</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>729148</v>
+        <v>729279</v>
       </c>
       <c r="R20" t="n">
-        <v>7389020</v>
+        <v>7388997</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119541243</v>
+        <v>119541257</v>
       </c>
       <c r="B21" t="n">
-        <v>57326</v>
+        <v>96868</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729279</v>
+        <v>729026</v>
       </c>
       <c r="R21" t="n">
-        <v>7388997</v>
+        <v>7389281</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119541297</v>
+        <v>119541206</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3850,25 +3850,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>729203</v>
+        <v>728984</v>
       </c>
       <c r="R33" t="n">
-        <v>7389019</v>
+        <v>7389224</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119541206</v>
+        <v>119541297</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>728984</v>
+        <v>729203</v>
       </c>
       <c r="R34" t="n">
-        <v>7389224</v>
+        <v>7389019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4144,10 +4144,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119541209</v>
+        <v>119541194</v>
       </c>
       <c r="B36" t="n">
-        <v>79115</v>
+        <v>87406</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>4412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729275</v>
+        <v>729247</v>
       </c>
       <c r="R36" t="n">
-        <v>7389001</v>
+        <v>7389213</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4228,7 +4228,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4247,10 +4246,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119541256</v>
+        <v>119541203</v>
       </c>
       <c r="B37" t="n">
-        <v>96868</v>
+        <v>79144</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4259,25 +4258,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4286,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>729155</v>
+        <v>729244</v>
       </c>
       <c r="R37" t="n">
-        <v>7389249</v>
+        <v>7389219</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,10 +4348,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119541194</v>
+        <v>119541209</v>
       </c>
       <c r="B38" t="n">
-        <v>87406</v>
+        <v>79115</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4364,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4412</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4388,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>729247</v>
+        <v>729275</v>
       </c>
       <c r="R38" t="n">
-        <v>7389213</v>
+        <v>7389001</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4433,6 +4432,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119541203</v>
+        <v>119541256</v>
       </c>
       <c r="B39" t="n">
-        <v>79144</v>
+        <v>96868</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4463,25 +4463,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729244</v>
+        <v>729155</v>
       </c>
       <c r="R39" t="n">
-        <v>7389219</v>
+        <v>7389249</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119541208</v>
+        <v>119541219</v>
       </c>
       <c r="B47" t="n">
-        <v>79115</v>
+        <v>86412</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5283,21 +5283,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>3690</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729190</v>
+        <v>729031</v>
       </c>
       <c r="R47" t="n">
-        <v>7389286</v>
+        <v>7389139</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,7 +5351,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5370,10 +5369,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119541267</v>
+        <v>119541266</v>
       </c>
       <c r="B48" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5386,21 +5385,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5410,10 +5409,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729230</v>
+        <v>729131</v>
       </c>
       <c r="R48" t="n">
-        <v>7389231</v>
+        <v>7389195</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,18 +5447,12 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5478,10 +5471,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119541241</v>
+        <v>119541205</v>
       </c>
       <c r="B49" t="n">
-        <v>57326</v>
+        <v>79144</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5494,21 +5487,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5518,10 +5511,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729213</v>
+        <v>729131</v>
       </c>
       <c r="R49" t="n">
-        <v>7389307</v>
+        <v>7389195</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,10 +5573,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119541219</v>
+        <v>119541290</v>
       </c>
       <c r="B50" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5592,25 +5585,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5613,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729031</v>
+        <v>729022</v>
       </c>
       <c r="R50" t="n">
-        <v>7389139</v>
+        <v>7389283</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5682,10 +5675,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119541266</v>
+        <v>119541300</v>
       </c>
       <c r="B51" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5694,25 +5687,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5722,10 +5715,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729131</v>
+        <v>729015</v>
       </c>
       <c r="R51" t="n">
-        <v>7389195</v>
+        <v>7389279</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5766,6 +5759,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5784,10 +5778,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119541205</v>
+        <v>119541208</v>
       </c>
       <c r="B52" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5800,21 +5794,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5824,10 +5818,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729131</v>
+        <v>729190</v>
       </c>
       <c r="R52" t="n">
-        <v>7389195</v>
+        <v>7389286</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5868,6 +5862,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5886,10 +5881,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119541290</v>
+        <v>119541267</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5898,25 +5893,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5926,10 +5921,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729022</v>
+        <v>729230</v>
       </c>
       <c r="R53" t="n">
-        <v>7389283</v>
+        <v>7389231</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5964,12 +5959,18 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5988,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119541300</v>
+        <v>119541241</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6000,25 +6001,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6028,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729015</v>
+        <v>729213</v>
       </c>
       <c r="R54" t="n">
-        <v>7389279</v>
+        <v>7389307</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6072,7 +6073,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6193,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119541213</v>
+        <v>119541235</v>
       </c>
       <c r="B56" t="n">
-        <v>86412</v>
+        <v>91884</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6209,21 +6209,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3690</v>
+        <v>5449</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729100</v>
+        <v>729331</v>
       </c>
       <c r="R56" t="n">
-        <v>7389150</v>
+        <v>7389160</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6295,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119541235</v>
+        <v>119541213</v>
       </c>
       <c r="B57" t="n">
-        <v>91884</v>
+        <v>86412</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6311,21 +6311,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>3690</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729331</v>
+        <v>729100</v>
       </c>
       <c r="R57" t="n">
-        <v>7389160</v>
+        <v>7389150</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7524,7 +7524,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119541264</v>
+        <v>119541268</v>
       </c>
       <c r="B69" t="n">
         <v>78262</v>
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>729223</v>
+        <v>729230</v>
       </c>
       <c r="R69" t="n">
-        <v>7389241</v>
+        <v>7389247</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7602,12 +7602,18 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7626,10 +7632,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119541268</v>
+        <v>119541289</v>
       </c>
       <c r="B70" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7638,25 +7644,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,10 +7672,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>729230</v>
+        <v>729031</v>
       </c>
       <c r="R70" t="n">
-        <v>7389247</v>
+        <v>7389263</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7704,18 +7710,12 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7734,10 +7734,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119541289</v>
+        <v>119541264</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7746,25 +7746,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7774,10 +7774,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>729031</v>
+        <v>729223</v>
       </c>
       <c r="R71" t="n">
-        <v>7389263</v>
+        <v>7389241</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7938,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119541274</v>
+        <v>119541202</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7950,25 +7950,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>729292</v>
+        <v>729249</v>
       </c>
       <c r="R73" t="n">
-        <v>7389205</v>
+        <v>7389192</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8040,7 +8040,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119541286</v>
+        <v>119541274</v>
       </c>
       <c r="B74" t="n">
         <v>91840</v>
@@ -8080,10 +8080,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>729172</v>
+        <v>729292</v>
       </c>
       <c r="R74" t="n">
-        <v>7389192</v>
+        <v>7389205</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8142,7 +8142,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119541282</v>
+        <v>119541286</v>
       </c>
       <c r="B75" t="n">
         <v>91840</v>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729120</v>
+        <v>729172</v>
       </c>
       <c r="R75" t="n">
-        <v>7389280</v>
+        <v>7389192</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8244,7 +8244,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119541273</v>
+        <v>119541282</v>
       </c>
       <c r="B76" t="n">
         <v>91840</v>
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>729321</v>
+        <v>729120</v>
       </c>
       <c r="R76" t="n">
-        <v>7389192</v>
+        <v>7389280</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119541284</v>
+        <v>119541273</v>
       </c>
       <c r="B77" t="n">
         <v>91840</v>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>729164</v>
+        <v>729321</v>
       </c>
       <c r="R77" t="n">
-        <v>7389239</v>
+        <v>7389192</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8448,10 +8448,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119541202</v>
+        <v>119541284</v>
       </c>
       <c r="B78" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8460,25 +8460,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8488,10 +8488,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>729249</v>
+        <v>729164</v>
       </c>
       <c r="R78" t="n">
-        <v>7389192</v>
+        <v>7389239</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 34593-2024 artfynd.xlsx
+++ b/artfynd/A 34593-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119541234</v>
+        <v>119541258</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>96868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729248</v>
+        <v>729030</v>
       </c>
       <c r="R2" t="n">
-        <v>7389111</v>
+        <v>7389117</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119541271</v>
+        <v>119541260</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>80483</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Själláriemgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729245</v>
+        <v>729227</v>
       </c>
       <c r="R3" t="n">
-        <v>7389062</v>
+        <v>7389252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119541191</v>
+        <v>119541298</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729250</v>
+        <v>729271</v>
       </c>
       <c r="R4" t="n">
-        <v>7389202</v>
+        <v>7388970</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119541288</v>
+        <v>119541203</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729066</v>
+        <v>729244</v>
       </c>
       <c r="R5" t="n">
-        <v>7389193</v>
+        <v>7389219</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119541231</v>
+        <v>119541288</v>
       </c>
       <c r="B6" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1099,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729190</v>
+        <v>729066</v>
       </c>
       <c r="R6" t="n">
-        <v>7389184</v>
+        <v>7389193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119541192</v>
+        <v>119541193</v>
       </c>
       <c r="B7" t="n">
         <v>88153</v>
@@ -1225,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729192</v>
+        <v>729066</v>
       </c>
       <c r="R7" t="n">
-        <v>7389302</v>
+        <v>7389193</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119541263</v>
+        <v>119541198</v>
       </c>
       <c r="B8" t="n">
-        <v>78262</v>
+        <v>87406</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729248</v>
+        <v>729161</v>
       </c>
       <c r="R8" t="n">
-        <v>7389196</v>
+        <v>7389019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119541236</v>
+        <v>119541252</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>96862</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1405,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729034</v>
+        <v>729140</v>
       </c>
       <c r="R9" t="n">
-        <v>7389252</v>
+        <v>7389338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119541204</v>
+        <v>119541286</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1507,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729234</v>
+        <v>729172</v>
       </c>
       <c r="R10" t="n">
-        <v>7389233</v>
+        <v>7389192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119541299</v>
+        <v>119541207</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1609,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729302</v>
+        <v>729102</v>
       </c>
       <c r="R11" t="n">
-        <v>7389005</v>
+        <v>7389109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119541245</v>
+        <v>119541257</v>
       </c>
       <c r="B12" t="n">
-        <v>91856</v>
+        <v>96868</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1711,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729274</v>
+        <v>729026</v>
       </c>
       <c r="R12" t="n">
-        <v>7389205</v>
+        <v>7389281</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119541258</v>
+        <v>119541215</v>
       </c>
       <c r="B13" t="n">
-        <v>96868</v>
+        <v>86412</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1813,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>3690</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729030</v>
+        <v>729329</v>
       </c>
       <c r="R13" t="n">
-        <v>7389117</v>
+        <v>7389121</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1881,6 +1885,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119541298</v>
+        <v>119541240</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729271</v>
+        <v>729204</v>
       </c>
       <c r="R14" t="n">
-        <v>7388970</v>
+        <v>7389007</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119541285</v>
+        <v>119541236</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729190</v>
+        <v>729034</v>
       </c>
       <c r="R15" t="n">
-        <v>7389208</v>
+        <v>7389252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119541296</v>
+        <v>119541232</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729148</v>
+        <v>729027</v>
       </c>
       <c r="R16" t="n">
-        <v>7389020</v>
+        <v>7389271</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119541250</v>
+        <v>119541241</v>
       </c>
       <c r="B17" t="n">
-        <v>91856</v>
+        <v>57326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729191</v>
+        <v>729213</v>
       </c>
       <c r="R17" t="n">
-        <v>7389198</v>
+        <v>7389307</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119541238</v>
+        <v>119541256</v>
       </c>
       <c r="B18" t="n">
-        <v>91884</v>
+        <v>96868</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729030</v>
+        <v>729155</v>
       </c>
       <c r="R18" t="n">
-        <v>7389117</v>
+        <v>7389249</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119541200</v>
+        <v>119541267</v>
       </c>
       <c r="B19" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>729251</v>
+        <v>729230</v>
       </c>
       <c r="R19" t="n">
-        <v>7389063</v>
+        <v>7389231</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,12 +2492,18 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2511,10 +2522,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119541243</v>
+        <v>119541220</v>
       </c>
       <c r="B20" t="n">
-        <v>57326</v>
+        <v>57463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2538,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>729279</v>
+        <v>729097</v>
       </c>
       <c r="R20" t="n">
-        <v>7388997</v>
+        <v>7389119</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119541257</v>
+        <v>119541287</v>
       </c>
       <c r="B21" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2640,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>729026</v>
+        <v>729086</v>
       </c>
       <c r="R21" t="n">
-        <v>7389281</v>
+        <v>7389202</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119541195</v>
+        <v>119541274</v>
       </c>
       <c r="B22" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2738,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>729146</v>
+        <v>729292</v>
       </c>
       <c r="R22" t="n">
-        <v>7389045</v>
+        <v>7389205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119541199</v>
+        <v>119541264</v>
       </c>
       <c r="B23" t="n">
-        <v>87406</v>
+        <v>78262</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2844,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>729173</v>
+        <v>729223</v>
       </c>
       <c r="R23" t="n">
-        <v>7389021</v>
+        <v>7389241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119541215</v>
+        <v>119541245</v>
       </c>
       <c r="B24" t="n">
-        <v>86412</v>
+        <v>91856</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2946,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>729329</v>
+        <v>729274</v>
       </c>
       <c r="R24" t="n">
-        <v>7389121</v>
+        <v>7389205</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,7 +3014,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3032,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119541252</v>
+        <v>119541276</v>
       </c>
       <c r="B25" t="n">
-        <v>96862</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,21 +3048,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3072,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729140</v>
+        <v>729228</v>
       </c>
       <c r="R25" t="n">
-        <v>7389338</v>
+        <v>7389283</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3124,10 +3134,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119541295</v>
+        <v>119541213</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>86412</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3136,25 +3146,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3164,10 +3174,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729099</v>
+        <v>729100</v>
       </c>
       <c r="R26" t="n">
-        <v>7389146</v>
+        <v>7389150</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3226,10 +3236,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119541244</v>
+        <v>119541212</v>
       </c>
       <c r="B27" t="n">
-        <v>91856</v>
+        <v>86412</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,21 +3252,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>3690</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3276,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>729255</v>
+        <v>729295</v>
       </c>
       <c r="R27" t="n">
-        <v>7389071</v>
+        <v>7389011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3328,10 +3338,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119541237</v>
+        <v>119541194</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>87406</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,21 +3354,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>4412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3368,10 +3378,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>729011</v>
+        <v>729247</v>
       </c>
       <c r="R28" t="n">
-        <v>7389279</v>
+        <v>7389213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119541276</v>
+        <v>119541191</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3442,25 +3452,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729228</v>
+        <v>729250</v>
       </c>
       <c r="R29" t="n">
-        <v>7389283</v>
+        <v>7389202</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3532,10 +3542,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119541279</v>
+        <v>119541239</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3544,25 +3554,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3572,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>729062</v>
+        <v>729192</v>
       </c>
       <c r="R30" t="n">
-        <v>7389313</v>
+        <v>7389008</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3634,10 +3644,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119541292</v>
+        <v>119541249</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3646,25 +3656,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3674,10 +3684,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>728973</v>
+        <v>728969</v>
       </c>
       <c r="R31" t="n">
-        <v>7389250</v>
+        <v>7389214</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3736,10 +3746,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119541251</v>
+        <v>119541206</v>
       </c>
       <c r="B32" t="n">
-        <v>91852</v>
+        <v>79144</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3748,25 +3758,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3776,10 +3786,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>729030</v>
+        <v>728984</v>
       </c>
       <c r="R32" t="n">
-        <v>7389117</v>
+        <v>7389224</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3848,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119541206</v>
+        <v>119541202</v>
       </c>
       <c r="B33" t="n">
         <v>79144</v>
@@ -3878,10 +3888,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>728984</v>
+        <v>729249</v>
       </c>
       <c r="R33" t="n">
-        <v>7389224</v>
+        <v>7389192</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,10 +3950,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119541297</v>
+        <v>119541263</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3952,25 +3962,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3980,10 +3990,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>729203</v>
+        <v>729248</v>
       </c>
       <c r="R34" t="n">
-        <v>7389019</v>
+        <v>7389196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4042,10 +4052,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119541253</v>
+        <v>119541217</v>
       </c>
       <c r="B35" t="n">
-        <v>96868</v>
+        <v>86412</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4054,25 +4064,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>3690</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4082,10 +4092,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729273</v>
+        <v>729203</v>
       </c>
       <c r="R35" t="n">
-        <v>7389025</v>
+        <v>7389017</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4126,6 +4136,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4144,10 +4155,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119541194</v>
+        <v>119541289</v>
       </c>
       <c r="B36" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4156,25 +4167,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4184,10 +4195,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729247</v>
+        <v>729031</v>
       </c>
       <c r="R36" t="n">
-        <v>7389213</v>
+        <v>7389263</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4246,10 +4257,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119541203</v>
+        <v>119541273</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4258,25 +4269,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4286,10 +4297,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>729244</v>
+        <v>729321</v>
       </c>
       <c r="R37" t="n">
-        <v>7389219</v>
+        <v>7389192</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4348,10 +4359,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119541209</v>
+        <v>119541275</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4360,25 +4371,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4388,10 +4399,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>729275</v>
+        <v>729277</v>
       </c>
       <c r="R38" t="n">
-        <v>7389001</v>
+        <v>7389208</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4432,7 +4443,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4451,10 +4461,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119541256</v>
+        <v>119541281</v>
       </c>
       <c r="B39" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4467,21 +4477,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4501,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>729155</v>
+        <v>729079</v>
       </c>
       <c r="R39" t="n">
-        <v>7389249</v>
+        <v>7389314</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,10 +4563,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119541291</v>
+        <v>119541251</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4569,21 +4579,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4593,10 +4603,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>729014</v>
+        <v>729030</v>
       </c>
       <c r="R40" t="n">
-        <v>7389291</v>
+        <v>7389117</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4655,10 +4665,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119541220</v>
+        <v>119541204</v>
       </c>
       <c r="B41" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4671,21 +4681,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4695,10 +4705,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729097</v>
+        <v>729234</v>
       </c>
       <c r="R41" t="n">
-        <v>7389119</v>
+        <v>7389233</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,10 +4767,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119541255</v>
+        <v>119541262</v>
       </c>
       <c r="B42" t="n">
-        <v>96868</v>
+        <v>78262</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4769,25 +4779,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4797,10 +4807,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>729136</v>
+        <v>729346</v>
       </c>
       <c r="R42" t="n">
-        <v>7389254</v>
+        <v>7389145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4859,10 +4869,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119541197</v>
+        <v>119541290</v>
       </c>
       <c r="B43" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4871,25 +4881,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4899,10 +4909,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729154</v>
+        <v>729022</v>
       </c>
       <c r="R43" t="n">
-        <v>7389019</v>
+        <v>7389283</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4971,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119541207</v>
+        <v>119541284</v>
       </c>
       <c r="B44" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4973,25 +4983,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5001,10 +5011,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>729102</v>
+        <v>729164</v>
       </c>
       <c r="R44" t="n">
-        <v>7389109</v>
+        <v>7389239</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5063,10 +5073,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119541278</v>
+        <v>119541205</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5075,25 +5085,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5103,10 +5113,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>729224</v>
+        <v>729131</v>
       </c>
       <c r="R45" t="n">
-        <v>7389317</v>
+        <v>7389195</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5165,10 +5175,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119541287</v>
+        <v>119541266</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5177,25 +5187,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5205,10 +5215,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>729086</v>
+        <v>729131</v>
       </c>
       <c r="R46" t="n">
-        <v>7389202</v>
+        <v>7389195</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5267,10 +5277,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119541219</v>
+        <v>119541255</v>
       </c>
       <c r="B47" t="n">
-        <v>86412</v>
+        <v>96868</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5279,25 +5289,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3690</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5307,10 +5317,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729031</v>
+        <v>729136</v>
       </c>
       <c r="R47" t="n">
-        <v>7389139</v>
+        <v>7389254</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5369,10 +5379,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119541266</v>
+        <v>119541196</v>
       </c>
       <c r="B48" t="n">
-        <v>78262</v>
+        <v>87406</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5385,21 +5395,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5409,10 +5419,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>729131</v>
+        <v>729151</v>
       </c>
       <c r="R48" t="n">
-        <v>7389195</v>
+        <v>7389037</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5471,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119541205</v>
+        <v>119541208</v>
       </c>
       <c r="B49" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5487,21 +5497,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5511,10 +5521,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>729131</v>
+        <v>729190</v>
       </c>
       <c r="R49" t="n">
-        <v>7389195</v>
+        <v>7389286</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5555,6 +5565,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5573,10 +5584,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119541290</v>
+        <v>119541195</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5585,25 +5596,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5613,10 +5624,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>729022</v>
+        <v>729146</v>
       </c>
       <c r="R50" t="n">
-        <v>7389283</v>
+        <v>7389045</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5675,7 +5686,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119541300</v>
+        <v>119541272</v>
       </c>
       <c r="B51" t="n">
         <v>91840</v>
@@ -5715,10 +5726,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>729015</v>
+        <v>729323</v>
       </c>
       <c r="R51" t="n">
-        <v>7389279</v>
+        <v>7389122</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5759,7 +5770,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5778,10 +5788,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119541208</v>
+        <v>119541216</v>
       </c>
       <c r="B52" t="n">
-        <v>79115</v>
+        <v>86412</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5794,21 +5804,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>3690</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5818,10 +5828,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>729190</v>
+        <v>729027</v>
       </c>
       <c r="R52" t="n">
-        <v>7389286</v>
+        <v>7389265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5881,10 +5891,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119541267</v>
+        <v>119541300</v>
       </c>
       <c r="B53" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5893,25 +5903,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5921,10 +5931,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>729230</v>
+        <v>729015</v>
       </c>
       <c r="R53" t="n">
-        <v>7389231</v>
+        <v>7389279</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5957,11 +5967,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5989,10 +5994,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119541241</v>
+        <v>119541295</v>
       </c>
       <c r="B54" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6001,25 +6006,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6029,10 +6034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>729213</v>
+        <v>729099</v>
       </c>
       <c r="R54" t="n">
-        <v>7389307</v>
+        <v>7389146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119541246</v>
+        <v>119541234</v>
       </c>
       <c r="B55" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6107,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6131,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>729182</v>
+        <v>729248</v>
       </c>
       <c r="R55" t="n">
-        <v>7389188</v>
+        <v>7389111</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6193,7 +6198,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119541235</v>
+        <v>119541238</v>
       </c>
       <c r="B56" t="n">
         <v>91884</v>
@@ -6233,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>729331</v>
+        <v>729030</v>
       </c>
       <c r="R56" t="n">
-        <v>7389160</v>
+        <v>7389117</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6295,10 +6300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119541213</v>
+        <v>119541293</v>
       </c>
       <c r="B57" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6307,25 +6312,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6335,10 +6340,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>729100</v>
+        <v>728966</v>
       </c>
       <c r="R57" t="n">
-        <v>7389150</v>
+        <v>7389240</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6397,10 +6402,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119541239</v>
+        <v>119541278</v>
       </c>
       <c r="B58" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6409,25 +6414,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6437,10 +6442,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>729192</v>
+        <v>729224</v>
       </c>
       <c r="R58" t="n">
-        <v>7389008</v>
+        <v>7389317</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6499,10 +6504,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119541260</v>
+        <v>119541299</v>
       </c>
       <c r="B59" t="n">
-        <v>80483</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6511,41 +6516,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Själláriemgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>729227</v>
+        <v>729302</v>
       </c>
       <c r="R59" t="n">
-        <v>7389252</v>
+        <v>7389005</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6572,12 +6574,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6586,7 +6588,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6605,10 +6606,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119541201</v>
+        <v>119541282</v>
       </c>
       <c r="B60" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6617,25 +6618,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6645,10 +6646,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>729236</v>
+        <v>729120</v>
       </c>
       <c r="R60" t="n">
-        <v>7389109</v>
+        <v>7389280</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6707,10 +6708,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119541232</v>
+        <v>119541237</v>
       </c>
       <c r="B61" t="n">
-        <v>91883</v>
+        <v>91884</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6723,21 +6724,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6747,10 +6748,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>729027</v>
+        <v>729011</v>
       </c>
       <c r="R61" t="n">
-        <v>7389271</v>
+        <v>7389279</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6809,10 +6810,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119541248</v>
+        <v>119541209</v>
       </c>
       <c r="B62" t="n">
-        <v>91856</v>
+        <v>79115</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6825,21 +6826,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6849,10 +6850,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>729004</v>
+        <v>729275</v>
       </c>
       <c r="R62" t="n">
-        <v>7389281</v>
+        <v>7389001</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6893,6 +6894,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6911,10 +6913,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119541249</v>
+        <v>119541283</v>
       </c>
       <c r="B63" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6923,25 +6925,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6951,10 +6953,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>728969</v>
+        <v>729151</v>
       </c>
       <c r="R63" t="n">
-        <v>7389214</v>
+        <v>7389249</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7013,10 +7015,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119541275</v>
+        <v>119541199</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7025,25 +7027,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7053,10 +7055,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>729277</v>
+        <v>729173</v>
       </c>
       <c r="R64" t="n">
-        <v>7389208</v>
+        <v>7389021</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7115,10 +7117,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119541272</v>
+        <v>119541192</v>
       </c>
       <c r="B65" t="n">
-        <v>91840</v>
+        <v>88153</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7127,25 +7129,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7155,10 +7157,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>729323</v>
+        <v>729192</v>
       </c>
       <c r="R65" t="n">
-        <v>7389122</v>
+        <v>7389302</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7217,10 +7219,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119541217</v>
+        <v>119541296</v>
       </c>
       <c r="B66" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7229,25 +7231,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7257,10 +7259,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>729203</v>
+        <v>729148</v>
       </c>
       <c r="R66" t="n">
-        <v>7389017</v>
+        <v>7389020</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7301,7 +7303,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7320,10 +7321,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119541193</v>
+        <v>119541243</v>
       </c>
       <c r="B67" t="n">
-        <v>88153</v>
+        <v>57326</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7336,21 +7337,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4962</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7360,10 +7361,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>729066</v>
+        <v>729279</v>
       </c>
       <c r="R67" t="n">
-        <v>7389193</v>
+        <v>7388997</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7422,10 +7423,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119541240</v>
+        <v>119541248</v>
       </c>
       <c r="B68" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7438,21 +7439,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7462,10 +7463,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>729204</v>
+        <v>729004</v>
       </c>
       <c r="R68" t="n">
-        <v>7389007</v>
+        <v>7389281</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7524,10 +7525,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119541268</v>
+        <v>119541246</v>
       </c>
       <c r="B69" t="n">
-        <v>78262</v>
+        <v>91856</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7540,21 +7541,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7564,10 +7565,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>729230</v>
+        <v>729182</v>
       </c>
       <c r="R69" t="n">
-        <v>7389247</v>
+        <v>7389188</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7602,18 +7603,12 @@
           <t>2024-08-30</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7632,7 +7627,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119541289</v>
+        <v>119541279</v>
       </c>
       <c r="B70" t="n">
         <v>91840</v>
@@ -7672,10 +7667,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>729031</v>
+        <v>729062</v>
       </c>
       <c r="R70" t="n">
-        <v>7389263</v>
+        <v>7389313</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7734,10 +7729,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119541264</v>
+        <v>119541291</v>
       </c>
       <c r="B71" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7746,25 +7741,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7774,10 +7769,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>729223</v>
+        <v>729014</v>
       </c>
       <c r="R71" t="n">
-        <v>7389241</v>
+        <v>7389291</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7836,10 +7831,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119541247</v>
+        <v>119541219</v>
       </c>
       <c r="B72" t="n">
-        <v>91856</v>
+        <v>86412</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7852,21 +7847,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2059</v>
+        <v>3690</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7876,10 +7871,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>729128</v>
+        <v>729031</v>
       </c>
       <c r="R72" t="n">
-        <v>7389194</v>
+        <v>7389139</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7938,10 +7933,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119541202</v>
+        <v>119541285</v>
       </c>
       <c r="B73" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7950,25 +7945,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7978,10 +7973,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>729249</v>
+        <v>729190</v>
       </c>
       <c r="R73" t="n">
-        <v>7389192</v>
+        <v>7389208</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8040,10 +8035,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119541274</v>
+        <v>119541253</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8056,21 +8051,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8080,10 +8075,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>729292</v>
+        <v>729273</v>
       </c>
       <c r="R74" t="n">
-        <v>7389205</v>
+        <v>7389025</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8142,10 +8137,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119541286</v>
+        <v>119541244</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8154,25 +8149,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8182,10 +8177,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>729172</v>
+        <v>729255</v>
       </c>
       <c r="R75" t="n">
-        <v>7389192</v>
+        <v>7389071</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8244,10 +8239,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119541282</v>
+        <v>119541200</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8256,25 +8251,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8284,10 +8279,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>729120</v>
+        <v>729251</v>
       </c>
       <c r="R76" t="n">
-        <v>7389280</v>
+        <v>7389063</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8346,10 +8341,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119541273</v>
+        <v>119541247</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8358,25 +8353,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8386,10 +8381,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>729321</v>
+        <v>729128</v>
       </c>
       <c r="R77" t="n">
-        <v>7389192</v>
+        <v>7389194</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8448,7 +8443,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119541284</v>
+        <v>119541271</v>
       </c>
       <c r="B78" t="n">
         <v>91840</v>
@@ -8488,10 +8483,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>729164</v>
+        <v>729245</v>
       </c>
       <c r="R78" t="n">
-        <v>7389239</v>
+        <v>7389062</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8550,10 +8545,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119541212</v>
+        <v>119541235</v>
       </c>
       <c r="B79" t="n">
-        <v>86412</v>
+        <v>91884</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8566,21 +8561,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3690</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8590,10 +8585,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>729295</v>
+        <v>729331</v>
       </c>
       <c r="R79" t="n">
-        <v>7389011</v>
+        <v>7389160</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8652,10 +8647,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119541196</v>
+        <v>119541292</v>
       </c>
       <c r="B80" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8664,25 +8659,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8692,10 +8687,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>729151</v>
+        <v>728973</v>
       </c>
       <c r="R80" t="n">
-        <v>7389037</v>
+        <v>7389250</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8754,10 +8749,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119541265</v>
+        <v>119541231</v>
       </c>
       <c r="B81" t="n">
-        <v>78262</v>
+        <v>91463</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8770,21 +8765,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>4745</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8794,10 +8789,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>729145</v>
+        <v>729190</v>
       </c>
       <c r="R81" t="n">
-        <v>7389330</v>
+        <v>7389184</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8856,10 +8851,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119541281</v>
+        <v>119541265</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8868,25 +8863,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8896,10 +8891,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>729079</v>
+        <v>729145</v>
       </c>
       <c r="R82" t="n">
-        <v>7389314</v>
+        <v>7389330</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8958,10 +8953,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119541293</v>
+        <v>119541268</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8970,25 +8965,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8998,10 +8993,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>728966</v>
+        <v>729230</v>
       </c>
       <c r="R83" t="n">
-        <v>7389240</v>
+        <v>7389247</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9036,12 +9031,18 @@
           <t>2024-08-30</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9060,10 +9061,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119541216</v>
+        <v>119541297</v>
       </c>
       <c r="B84" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9072,25 +9073,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9100,10 +9101,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>729027</v>
+        <v>729203</v>
       </c>
       <c r="R84" t="n">
-        <v>7389265</v>
+        <v>7389019</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9144,7 +9145,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9163,10 +9163,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119541283</v>
+        <v>119541197</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9175,25 +9175,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>729151</v>
+        <v>729154</v>
       </c>
       <c r="R85" t="n">
-        <v>7389249</v>
+        <v>7389019</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9265,10 +9265,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119541262</v>
+        <v>119541250</v>
       </c>
       <c r="B86" t="n">
-        <v>78262</v>
+        <v>91856</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9281,21 +9281,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9305,10 +9305,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>729346</v>
+        <v>729191</v>
       </c>
       <c r="R86" t="n">
-        <v>7389145</v>
+        <v>7389198</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9367,10 +9367,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119541198</v>
+        <v>119541201</v>
       </c>
       <c r="B87" t="n">
-        <v>87406</v>
+        <v>79144</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9383,21 +9383,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4412</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>729161</v>
+        <v>729236</v>
       </c>
       <c r="R87" t="n">
-        <v>7389019</v>
+        <v>7389109</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
